--- a/markets/network/dist/20261026_AI網通市場模型_v0.2.3.xlsx
+++ b/markets/network/dist/20261026_AI網通市場模型_v0.2.3.xlsx
@@ -207,13 +207,29 @@
     <definedName function="false" hidden="false" name="c_VR_su_sw_hi" vbProcedure="false">In!$F$44</definedName>
     <definedName function="false" hidden="false" name="c_VR_su_sw_lo" vbProcedure="false">In!$D$44</definedName>
     <definedName function="false" hidden="false" name="g29_amd" vbProcedure="false">In!$E$24</definedName>
+    <definedName function="false" hidden="false" name="g29_amd_hi" vbProcedure="false">In!$F$24</definedName>
+    <definedName function="false" hidden="false" name="g29_amd_lo" vbProcedure="false">In!$D$24</definedName>
     <definedName function="false" hidden="false" name="g29_bw" vbProcedure="false">In!$E$8</definedName>
+    <definedName function="false" hidden="false" name="g29_bw_hi" vbProcedure="false">In!$F$8</definedName>
+    <definedName function="false" hidden="false" name="g29_bw_lo" vbProcedure="false">In!$D$8</definedName>
     <definedName function="false" hidden="false" name="g29_hp" vbProcedure="false">In!$E$20</definedName>
+    <definedName function="false" hidden="false" name="g29_hp_hi" vbProcedure="false">In!$F$20</definedName>
+    <definedName function="false" hidden="false" name="g29_hp_lo" vbProcedure="false">In!$D$20</definedName>
     <definedName function="false" hidden="false" name="g29_oth" vbProcedure="false">In!$E$36</definedName>
+    <definedName function="false" hidden="false" name="g29_oth_hi" vbProcedure="false">In!$F$36</definedName>
+    <definedName function="false" hidden="false" name="g29_oth_lo" vbProcedure="false">In!$D$36</definedName>
     <definedName function="false" hidden="false" name="g29_rb" vbProcedure="false">In!$E$12</definedName>
+    <definedName function="false" hidden="false" name="g29_rb_hi" vbProcedure="false">In!$F$12</definedName>
+    <definedName function="false" hidden="false" name="g29_rb_lo" vbProcedure="false">In!$D$12</definedName>
     <definedName function="false" hidden="false" name="g29_ru" vbProcedure="false">In!$E$16</definedName>
+    <definedName function="false" hidden="false" name="g29_ru_hi" vbProcedure="false">In!$F$16</definedName>
+    <definedName function="false" hidden="false" name="g29_ru_lo" vbProcedure="false">In!$D$16</definedName>
     <definedName function="false" hidden="false" name="g29_tpu" vbProcedure="false">In!$E$28</definedName>
+    <definedName function="false" hidden="false" name="g29_tpu_hi" vbProcedure="false">In!$F$28</definedName>
+    <definedName function="false" hidden="false" name="g29_tpu_lo" vbProcedure="false">In!$D$28</definedName>
     <definedName function="false" hidden="false" name="g29_trn" vbProcedure="false">In!$E$32</definedName>
+    <definedName function="false" hidden="false" name="g29_trn_hi" vbProcedure="false">In!$F$32</definedName>
+    <definedName function="false" hidden="false" name="g29_trn_lo" vbProcedure="false">In!$D$32</definedName>
     <definedName function="false" hidden="false" name="it_AMD8" vbProcedure="false">In!$E$97</definedName>
     <definedName function="false" hidden="false" name="it_AMDR" vbProcedure="false">In!$E$98</definedName>
     <definedName function="false" hidden="false" name="it_ASIC" vbProcedure="false">In!$E$101</definedName>
@@ -2786,6 +2802,25 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">Siliconomics v0.2 SIF_g29_bw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（單一來源；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">2029 </t>
     </r>
     <r>
@@ -2795,7 +2830,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">無顆數預測</t>
+      <t xml:space="preserve">無平台別顆數預測，區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±10pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -18529,8 +18583,14 @@
       <c r="C8" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D8" s="7" t="n">
+        <v>-0.7</v>
+      </c>
       <c r="E8" s="7" t="n">
         <v>-0.5</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>-0.3</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>35</v>
@@ -18609,14 +18669,20 @@
       <c r="C12" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D12" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E12" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F12" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>36</v>
+      <c r="H12" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18689,14 +18755,20 @@
       <c r="C16" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D16" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E16" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F16" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>36</v>
+      <c r="H16" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18769,14 +18841,20 @@
       <c r="C20" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G20" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="8" t="s">
-        <v>36</v>
+      <c r="H20" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18849,14 +18927,20 @@
       <c r="C24" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D24" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E24" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F24" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G24" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="8" t="s">
-        <v>36</v>
+      <c r="H24" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18929,14 +19013,20 @@
       <c r="C28" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D28" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E28" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F28" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G28" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>36</v>
+      <c r="H28" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19009,14 +19099,20 @@
       <c r="C32" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D32" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E32" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F32" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G32" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>36</v>
+      <c r="H32" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19089,14 +19185,20 @@
       <c r="C36" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D36" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E36" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F36" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G36" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H36" s="8" t="s">
-        <v>36</v>
+      <c r="H36" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/markets/network/dist/20261026_AI網通市場模型_v0.2.3.xlsx
+++ b/markets/network/dist/20261026_AI網通市場模型_v0.2.3.xlsx
@@ -2802,7 +2802,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Siliconomics v0.2 SIF_g29_bw</t>
+      <t xml:space="preserve">Siliconomics SIF_g29_bw</t>
     </r>
     <r>
       <rPr>

--- a/markets/network/dist/20261026_AI網通市場模型_v0.2.3.xlsx
+++ b/markets/network/dist/20261026_AI網通市場模型_v0.2.3.xlsx
@@ -33,17 +33,41 @@
     <definedName function="false" hidden="false" name="cpo_28" vbProcedure="false">In!$E$105</definedName>
     <definedName function="false" hidden="false" name="cpo_29" vbProcedure="false">In!$E$106</definedName>
     <definedName function="false" hidden="false" name="cpo_A_26" vbProcedure="false">In!$E$125</definedName>
+    <definedName function="false" hidden="false" name="cpo_A_26_hi" vbProcedure="false">In!$F$125</definedName>
+    <definedName function="false" hidden="false" name="cpo_A_26_lo" vbProcedure="false">In!$D$125</definedName>
     <definedName function="false" hidden="false" name="cpo_A_27" vbProcedure="false">In!$E$126</definedName>
+    <definedName function="false" hidden="false" name="cpo_A_27_hi" vbProcedure="false">In!$F$126</definedName>
+    <definedName function="false" hidden="false" name="cpo_A_27_lo" vbProcedure="false">In!$D$126</definedName>
     <definedName function="false" hidden="false" name="cpo_A_28" vbProcedure="false">In!$E$127</definedName>
+    <definedName function="false" hidden="false" name="cpo_A_28_hi" vbProcedure="false">In!$F$127</definedName>
+    <definedName function="false" hidden="false" name="cpo_A_28_lo" vbProcedure="false">In!$D$127</definedName>
     <definedName function="false" hidden="false" name="cpo_A_29" vbProcedure="false">In!$E$128</definedName>
+    <definedName function="false" hidden="false" name="cpo_A_29_hi" vbProcedure="false">In!$F$128</definedName>
+    <definedName function="false" hidden="false" name="cpo_A_29_lo" vbProcedure="false">In!$D$128</definedName>
     <definedName function="false" hidden="false" name="cpo_B_26" vbProcedure="false">In!$E$129</definedName>
+    <definedName function="false" hidden="false" name="cpo_B_26_hi" vbProcedure="false">In!$F$129</definedName>
+    <definedName function="false" hidden="false" name="cpo_B_26_lo" vbProcedure="false">In!$D$129</definedName>
     <definedName function="false" hidden="false" name="cpo_B_27" vbProcedure="false">In!$E$130</definedName>
+    <definedName function="false" hidden="false" name="cpo_B_27_hi" vbProcedure="false">In!$F$130</definedName>
+    <definedName function="false" hidden="false" name="cpo_B_27_lo" vbProcedure="false">In!$D$130</definedName>
     <definedName function="false" hidden="false" name="cpo_B_28" vbProcedure="false">In!$E$131</definedName>
+    <definedName function="false" hidden="false" name="cpo_B_28_hi" vbProcedure="false">In!$F$131</definedName>
+    <definedName function="false" hidden="false" name="cpo_B_28_lo" vbProcedure="false">In!$D$131</definedName>
     <definedName function="false" hidden="false" name="cpo_B_29" vbProcedure="false">In!$E$132</definedName>
+    <definedName function="false" hidden="false" name="cpo_B_29_hi" vbProcedure="false">In!$F$132</definedName>
+    <definedName function="false" hidden="false" name="cpo_B_29_lo" vbProcedure="false">In!$D$132</definedName>
     <definedName function="false" hidden="false" name="cpo_C_26" vbProcedure="false">In!$E$133</definedName>
+    <definedName function="false" hidden="false" name="cpo_C_26_hi" vbProcedure="false">In!$F$133</definedName>
+    <definedName function="false" hidden="false" name="cpo_C_26_lo" vbProcedure="false">In!$D$133</definedName>
     <definedName function="false" hidden="false" name="cpo_C_27" vbProcedure="false">In!$E$134</definedName>
+    <definedName function="false" hidden="false" name="cpo_C_27_hi" vbProcedure="false">In!$F$134</definedName>
+    <definedName function="false" hidden="false" name="cpo_C_27_lo" vbProcedure="false">In!$D$134</definedName>
     <definedName function="false" hidden="false" name="cpo_C_28" vbProcedure="false">In!$E$135</definedName>
+    <definedName function="false" hidden="false" name="cpo_C_28_hi" vbProcedure="false">In!$F$135</definedName>
+    <definedName function="false" hidden="false" name="cpo_C_28_lo" vbProcedure="false">In!$D$135</definedName>
     <definedName function="false" hidden="false" name="cpo_C_29" vbProcedure="false">In!$E$136</definedName>
+    <definedName function="false" hidden="false" name="cpo_C_29_hi" vbProcedure="false">In!$F$136</definedName>
+    <definedName function="false" hidden="false" name="cpo_C_29_lo" vbProcedure="false">In!$D$136</definedName>
     <definedName function="false" hidden="false" name="c_AMD8_nic" vbProcedure="false">In!$E$67</definedName>
     <definedName function="false" hidden="false" name="c_AMD8_nic_hi" vbProcedure="false">In!$F$67</definedName>
     <definedName function="false" hidden="false" name="c_AMD8_nic_lo" vbProcedure="false">In!$D$67</definedName>
@@ -231,13 +255,23 @@
     <definedName function="false" hidden="false" name="g29_trn_hi" vbProcedure="false">In!$F$32</definedName>
     <definedName function="false" hidden="false" name="g29_trn_lo" vbProcedure="false">In!$D$32</definedName>
     <definedName function="false" hidden="false" name="it_AMD8" vbProcedure="false">In!$E$97</definedName>
+    <definedName function="false" hidden="false" name="it_AMD8_hi" vbProcedure="false">In!$F$97</definedName>
+    <definedName function="false" hidden="false" name="it_AMD8_lo" vbProcedure="false">In!$D$97</definedName>
     <definedName function="false" hidden="false" name="it_AMDR" vbProcedure="false">In!$E$98</definedName>
+    <definedName function="false" hidden="false" name="it_AMDR_hi" vbProcedure="false">In!$F$98</definedName>
+    <definedName function="false" hidden="false" name="it_AMDR_lo" vbProcedure="false">In!$D$98</definedName>
     <definedName function="false" hidden="false" name="it_ASIC" vbProcedure="false">In!$E$101</definedName>
+    <definedName function="false" hidden="false" name="it_ASIC_hi" vbProcedure="false">In!$F$101</definedName>
+    <definedName function="false" hidden="false" name="it_ASIC_lo" vbProcedure="false">In!$D$101</definedName>
     <definedName function="false" hidden="false" name="it_GB" vbProcedure="false">In!$E$93</definedName>
     <definedName function="false" hidden="false" name="it_HP" vbProcedure="false">In!$E$96</definedName>
     <definedName function="false" hidden="false" name="it_RU" vbProcedure="false">In!$E$95</definedName>
     <definedName function="false" hidden="false" name="it_TPU" vbProcedure="false">In!$E$99</definedName>
+    <definedName function="false" hidden="false" name="it_TPU_hi" vbProcedure="false">In!$F$99</definedName>
+    <definedName function="false" hidden="false" name="it_TPU_lo" vbProcedure="false">In!$D$99</definedName>
     <definedName function="false" hidden="false" name="it_TRN" vbProcedure="false">In!$E$100</definedName>
+    <definedName function="false" hidden="false" name="it_TRN_hi" vbProcedure="false">In!$F$100</definedName>
+    <definedName function="false" hidden="false" name="it_TRN_lo" vbProcedure="false">In!$D$100</definedName>
     <definedName function="false" hidden="false" name="it_VR" vbProcedure="false">In!$E$94</definedName>
     <definedName function="false" hidden="false" name="nv_opt" vbProcedure="false">In!$E$115</definedName>
     <definedName function="false" hidden="false" name="nv_opt_hi" vbProcedure="false">In!$F$115</definedName>
@@ -257,9 +291,17 @@
     <definedName function="false" hidden="false" name="rep_nv26_lo" vbProcedure="false">In!$D$120</definedName>
     <definedName function="false" hidden="false" name="rep_opt26" vbProcedure="false">In!$E$122</definedName>
     <definedName function="false" hidden="false" name="suopt_26" vbProcedure="false">In!$E$107</definedName>
+    <definedName function="false" hidden="false" name="suopt_26_hi" vbProcedure="false">In!$F$107</definedName>
+    <definedName function="false" hidden="false" name="suopt_26_lo" vbProcedure="false">In!$D$107</definedName>
     <definedName function="false" hidden="false" name="suopt_27" vbProcedure="false">In!$E$108</definedName>
+    <definedName function="false" hidden="false" name="suopt_27_hi" vbProcedure="false">In!$F$108</definedName>
+    <definedName function="false" hidden="false" name="suopt_27_lo" vbProcedure="false">In!$D$108</definedName>
     <definedName function="false" hidden="false" name="suopt_28" vbProcedure="false">In!$E$109</definedName>
+    <definedName function="false" hidden="false" name="suopt_28_hi" vbProcedure="false">In!$F$109</definedName>
+    <definedName function="false" hidden="false" name="suopt_28_lo" vbProcedure="false">In!$D$109</definedName>
     <definedName function="false" hidden="false" name="suopt_29" vbProcedure="false">In!$E$110</definedName>
+    <definedName function="false" hidden="false" name="suopt_29_hi" vbProcedure="false">In!$F$110</definedName>
+    <definedName function="false" hidden="false" name="suopt_29_lo" vbProcedure="false">In!$D$110</definedName>
     <definedName function="false" hidden="false" name="su_cu" vbProcedure="false">In!$E$111</definedName>
     <definedName function="false" hidden="false" name="su_cu_hi" vbProcedure="false">In!$F$111</definedName>
     <definedName function="false" hidden="false" name="su_cu_lo" vbProcedure="false">In!$D$111</definedName>
@@ -298,7 +340,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="453">
   <si>
     <r>
       <rPr>
@@ -9959,26 +10001,121 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Tokenomics v20.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">v19.0 </t>
+      <t xml:space="preserve">Tokenomics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TK_In </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁鏡像）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IF_CapexIT ÷ IF_GPUsPerGW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，基準成本情境）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起改為公式（原寫死 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v20.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值，基準與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v21.7 </t>
     </r>
     <r>
       <rPr>
@@ -9989,15 +10126,20 @@
       </rPr>
       <t xml:space="preserve">相同）</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IF_CapexIT 32.237 $B ÷ 487,008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it_VR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200 NVL72</t>
     </r>
     <r>
       <rPr>
@@ -10016,50 +10158,38 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v5.27 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">37.445</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">it_VR</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200 NVL72</t>
+      <t xml:space="preserve">Rubin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">） </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT capex</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics</t>
     </r>
     <r>
       <rPr>
@@ -10078,7 +10208,164 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Rubin</t>
+      <t xml:space="preserve">TK_In </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁鏡像）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IF_CapexIT ÷ IF_GPUsPerGW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，基準成本情境）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起改為公式（原寫死 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v20.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值，基準與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v21.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相同）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">it_RU</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin Ultra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MGX </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">單架／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NVL576</t>
     </r>
     <r>
       <rPr>
@@ -10101,21 +10388,15 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">37.586 ÷ 291,744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">it_RU</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin Ultra</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics</t>
     </r>
     <r>
       <rPr>
@@ -10134,26 +10415,145 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MGX </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">單架／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NVL576</t>
+      <t xml:space="preserve">TK_In </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁鏡像）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IF_CapexIT ÷ IF_GPUsPerGW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，基準成本情境）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起改為公式（原寫死 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v20.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值，基準與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v21.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相同）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">it_HP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Hopper HGX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 GPU</t>
     </r>
     <r>
       <rPr>
@@ -10176,21 +10576,15 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">50.086 ÷ 194,760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">it_HP</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Hopper HGX</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics</t>
     </r>
     <r>
       <rPr>
@@ -10209,16 +10603,154 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8 GPU</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">） </t>
+      <t xml:space="preserve">TK_In </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁鏡像）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IF_CapexIT ÷ IF_GPUsPerGW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，基準成本情境）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起改為公式（原寫死 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v20.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值，基準與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v21.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相同）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">it_AMD8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AMD MI355</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伺服器） </t>
     </r>
     <r>
       <rPr>
@@ -10232,21 +10764,129 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">27.510 ÷ 718,048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">it_AMD8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AMD MI355</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AMD MI355 8 GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伺服器每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT capex </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無公開值；比照 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Hopper HGX </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">量級（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics H100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">38K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）上調；區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30–50</t>
     </r>
     <r>
       <rPr>
@@ -10265,16 +10905,59 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8 GPU </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伺服器） </t>
+      <t xml:space="preserve">v0.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">補）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">it_AMDR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AMD Helios</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MI455X </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機架） </t>
     </r>
     <r>
       <rPr>
@@ -10288,18 +10971,175 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">it_AMDR</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AMD Helios</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">it_TPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google TPU IT capex</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TPU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trainium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT capex</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝伺服器與機架總價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數，無公開值；量級約為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
     </r>
     <r>
       <rPr>
@@ -10318,73 +11158,74 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MI455X </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機架） </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT capex</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">it_TPU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google TPU IT capex</t>
+      <t xml:space="preserve">Tokenomics </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">66K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.3–0.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍；區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">補</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">it_TRN</t>
@@ -11176,7 +12017,55 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">後）</t>
+      <t xml:space="preserve">後）。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">補）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 0–5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 10–30%</t>
     </r>
   </si>
   <si>
@@ -13078,6 +13967,44 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">2028 8–14%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">補）：各年基準 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×0.7–×1.4</t>
     </r>
   </si>
   <si>
@@ -20705,95 +21632,137 @@
       <c r="C97" s="0" t="s">
         <v>226</v>
       </c>
+      <c r="D97" s="7" t="n">
+        <v>30</v>
+      </c>
       <c r="E97" s="7" t="n">
         <v>40</v>
       </c>
+      <c r="F97" s="7" t="n">
+        <v>50</v>
+      </c>
       <c r="G97" s="8" t="s">
         <v>35</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C98" s="0" t="s">
         <v>226</v>
       </c>
+      <c r="D98" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="E98" s="7" t="n">
         <v>100</v>
       </c>
+      <c r="F98" s="7" t="n">
+        <v>120</v>
+      </c>
       <c r="G98" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C99" s="0" t="s">
         <v>226</v>
       </c>
+      <c r="D99" s="7" t="n">
+        <v>15</v>
+      </c>
       <c r="E99" s="7" t="n">
         <v>25</v>
       </c>
+      <c r="F99" s="7" t="n">
+        <v>35</v>
+      </c>
       <c r="G99" s="8" t="s">
         <v>35</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C100" s="0" t="s">
         <v>226</v>
       </c>
+      <c r="D100" s="7" t="n">
+        <v>12</v>
+      </c>
       <c r="E100" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="F100" s="7" t="n">
+        <v>30</v>
+      </c>
       <c r="G100" s="8" t="s">
         <v>35</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C101" s="0" t="s">
         <v>226</v>
       </c>
+      <c r="D101" s="7" t="n">
+        <v>12</v>
+      </c>
       <c r="E101" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="F101" s="7" t="n">
+        <v>30</v>
+      </c>
       <c r="G101" s="8" t="s">
         <v>35</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C103" s="0" t="s">
         <v>34</v>
@@ -20806,15 +21775,15 @@
         <v>106</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C104" s="0" t="s">
         <v>34</v>
@@ -20832,10 +21801,10 @@
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C105" s="0" t="s">
         <v>34</v>
@@ -20853,10 +21822,10 @@
     </row>
     <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C106" s="0" t="s">
         <v>34</v>
@@ -20874,35 +21843,47 @@
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C107" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D107" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E107" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="F107" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G107" s="8" t="s">
         <v>66</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D108" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="8" t="s">
@@ -20914,16 +21895,22 @@
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C109" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D109" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E109" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>0.05</v>
       </c>
       <c r="G109" s="8" t="s">
         <v>66</v>
@@ -20934,16 +21921,22 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C110" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D110" s="7" t="n">
+        <v>0.1</v>
+      </c>
       <c r="E110" s="7" t="n">
         <v>0.2</v>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>0.3</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>66</v>
@@ -20954,10 +21947,10 @@
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C111" s="0" t="s">
         <v>34</v>
@@ -20975,20 +21968,20 @@
         <v>35</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>34</v>
@@ -21006,15 +21999,15 @@
         <v>35</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C114" s="0" t="s">
         <v>34</v>
@@ -21032,15 +22025,15 @@
         <v>66</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C115" s="0" t="s">
         <v>34</v>
@@ -21060,10 +22053,10 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C116" s="0" t="s">
         <v>34</v>
@@ -21081,15 +22074,15 @@
         <v>35</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C117" s="0" t="s">
         <v>34</v>
@@ -21107,15 +22100,15 @@
         <v>35</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C118" s="0" t="s">
         <v>34</v>
@@ -21135,10 +22128,10 @@
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C119" s="0" t="s">
         <v>34</v>
@@ -21158,13 +22151,13 @@
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>68</v>
@@ -21176,21 +22169,21 @@
         <v>80</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H120" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>16</v>
@@ -21205,18 +22198,18 @@
         <v>106</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E122" s="7" t="n">
         <v>26</v>
@@ -21225,15 +22218,15 @@
         <v>25</v>
       </c>
       <c r="H122" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C123" s="0" t="s">
         <v>34</v>
@@ -21245,49 +22238,61 @@
         <v>25</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C125" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D125" s="7" t="n">
+        <v>0.007</v>
+      </c>
       <c r="E125" s="7" t="n">
         <v>0.01</v>
       </c>
+      <c r="F125" s="7" t="n">
+        <v>0.014</v>
+      </c>
       <c r="G125" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C126" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D126" s="7" t="n">
+        <v>0.035</v>
+      </c>
       <c r="E126" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F126" s="7" t="n">
+        <v>0.07</v>
+      </c>
       <c r="G126" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>29</v>
@@ -21295,19 +22300,25 @@
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C127" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D127" s="7" t="n">
+        <v>0.07</v>
+      </c>
       <c r="E127" s="7" t="n">
         <v>0.1</v>
       </c>
+      <c r="F127" s="7" t="n">
+        <v>0.14</v>
+      </c>
       <c r="G127" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H127" s="6" t="s">
         <v>29</v>
@@ -21315,19 +22326,25 @@
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C128" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D128" s="7" t="n">
+        <v>0.112</v>
+      </c>
       <c r="E128" s="7" t="n">
         <v>0.16</v>
       </c>
+      <c r="F128" s="7" t="n">
+        <v>0.224</v>
+      </c>
       <c r="G128" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H128" s="6" t="s">
         <v>29</v>
@@ -21335,39 +22352,51 @@
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C129" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D129" s="7" t="n">
+        <v>0.007</v>
+      </c>
       <c r="E129" s="7" t="n">
         <v>0.01</v>
       </c>
+      <c r="F129" s="7" t="n">
+        <v>0.014</v>
+      </c>
       <c r="G129" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C130" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D130" s="7" t="n">
+        <v>0.021</v>
+      </c>
       <c r="E130" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F130" s="7" t="n">
+        <v>0.042</v>
+      </c>
       <c r="G130" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H130" s="6" t="s">
         <v>29</v>
@@ -21375,19 +22404,25 @@
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C131" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D131" s="7" t="n">
+        <v>0.035</v>
+      </c>
       <c r="E131" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F131" s="7" t="n">
+        <v>0.07</v>
+      </c>
       <c r="G131" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H131" s="6" t="s">
         <v>29</v>
@@ -21395,19 +22430,25 @@
     </row>
     <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C132" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D132" s="7" t="n">
+        <v>0.056</v>
+      </c>
       <c r="E132" s="7" t="n">
         <v>0.08</v>
       </c>
+      <c r="F132" s="7" t="n">
+        <v>0.112</v>
+      </c>
       <c r="G132" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>29</v>
@@ -21415,36 +22456,48 @@
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C133" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D133" s="7" t="n">
+        <v>0.007</v>
+      </c>
       <c r="E133" s="7" t="n">
         <v>0.01</v>
       </c>
+      <c r="F133" s="7" t="n">
+        <v>0.014</v>
+      </c>
       <c r="G133" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C134" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D134" s="7" t="n">
+        <v>0.014</v>
+      </c>
       <c r="E134" s="7" t="n">
         <v>0.02</v>
+      </c>
+      <c r="F134" s="7" t="n">
+        <v>0.028</v>
       </c>
       <c r="G134" s="8" t="s">
         <v>35</v>
@@ -21455,16 +22508,22 @@
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C135" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D135" s="7" t="n">
+        <v>0.021</v>
+      </c>
       <c r="E135" s="7" t="n">
         <v>0.03</v>
+      </c>
+      <c r="F135" s="7" t="n">
+        <v>0.042</v>
       </c>
       <c r="G135" s="8" t="s">
         <v>35</v>
@@ -21475,16 +22534,22 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C136" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="D136" s="7" t="n">
+        <v>0.035</v>
+      </c>
       <c r="E136" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F136" s="7" t="n">
+        <v>0.07</v>
       </c>
       <c r="G136" s="8" t="s">
         <v>35</v>
@@ -21518,32 +22583,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B4" s="10" t="n">
         <f aca="false">u_bw_26</f>
@@ -21562,12 +22627,12 @@
         <v>0.25</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B5" s="10" t="n">
         <f aca="false">u_rb_26</f>
@@ -21586,12 +22651,12 @@
         <v>8.05</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">u_ru_26</f>
@@ -21610,12 +22675,12 @@
         <v>2.3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">u_hp_26</f>
@@ -21634,12 +22699,12 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B8" s="10" t="n">
         <f aca="false">u_amd_26</f>
@@ -21658,12 +22723,12 @@
         <v>2.3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">u_tpu_26</f>
@@ -21682,12 +22747,12 @@
         <v>8.05</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">u_trn_26</f>
@@ -21706,12 +22771,12 @@
         <v>3.45</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B11" s="10" t="n">
         <f aca="false">u_oth_26</f>
@@ -21730,12 +22795,12 @@
         <v>5.75</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">SUM(B4:B11)</f>
@@ -21780,7 +22845,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21791,32 +22856,32 @@
         <v>15</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_su_sw+Units!B5*c_VR_su_sw+Units!B6*c_RU_su_sw+Units!B7*c_HP_su_sw+Units!B8*c_AMD8_su_sw+Units!B9*c_TPU_su_sw+Units!B10*c_TRN_su_sw+Units!B11*c_ASIC_su_sw)/1000</f>
@@ -21837,10 +22902,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C6" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_su_ic+Units!B5*c_VR_su_ic+Units!B6*c_RU_su_ic+Units!B7*c_HP_su_ic+Units!B8*c_AMD8_su_ic+Units!B9*c_TPU_su_ic+Units!B10*c_TRN_su_ic+Units!B11*c_ASIC_su_ic)/1000</f>
@@ -21861,10 +22926,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_so_sw+Units!B5*c_VR_so_sw+Units!B6*c_RU_so_sw+Units!B7*c_HP_so_sw+Units!B8*c_AMD8_so_sw+Units!B9*c_TPU_so_sw+Units!B10*c_TRN_so_sw+Units!B11*c_ASIC_so_sw)/1000</f>
@@ -21885,10 +22950,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_so_opt+Units!B5*c_VR_so_opt+Units!B6*c_RU_so_opt+Units!B7*c_HP_so_opt+Units!B8*c_AMD8_so_opt+Units!B9*c_TPU_so_opt+Units!B10*c_TRN_so_opt+Units!B11*c_ASIC_so_opt)/1000</f>
@@ -21909,10 +22974,10 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_so_cu+Units!B5*c_VR_so_cu+Units!B6*c_RU_so_cu+Units!B7*c_HP_so_cu+Units!B8*c_AMD8_so_cu+Units!B9*c_TPU_so_cu+Units!B10*c_TRN_so_cu+Units!B11*c_ASIC_so_cu)/1000</f>
@@ -21933,10 +22998,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_nic+Units!B5*c_VR_nic+Units!B6*c_RU_nic+Units!B7*c_HP_nic+Units!B8*c_AMD8_nic+Units!B9*c_TPU_nic+Units!B10*c_TRN_nic+Units!B11*c_ASIC_nic)/1000</f>
@@ -21957,10 +23022,10 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -21981,7 +23046,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>34</v>
@@ -22001,7 +23066,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>34</v>
@@ -22023,12 +23088,12 @@
         <v>0.279104336238518</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>34</v>
@@ -22052,15 +23117,15 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C17" s="11" t="n">
         <f aca="false">C5+C7</f>
@@ -22081,10 +23146,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">C8+C6*suopt_26</f>
@@ -22105,10 +23170,10 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C19" s="11" t="n">
         <f aca="false">C8*cpo_26</f>
@@ -22129,10 +23194,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C20" s="11" t="n">
         <f aca="false">C18-C19</f>
@@ -22153,10 +23218,10 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">C9+C6*(1-suopt_26)*su_cu</f>
@@ -22177,10 +23242,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C22" s="11" t="n">
         <f aca="false">C6*(1-suopt_26)*(1-su_cu)</f>
@@ -22201,10 +23266,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C23" s="11" t="n">
         <f aca="false">C10</f>
@@ -22225,10 +23290,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">C17+C18+C21+C22+C23-C11</f>
@@ -22249,19 +23314,19 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C27" s="11" t="n">
         <f aca="false">(Units!B4*it_GB+Units!B5*it_VR+Units!B6*it_RU+Units!B7*it_HP+Units!B8*it_AMD8+Units!B9*it_TPU+Units!B10*it_TRN+Units!B11*it_ASIC)</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="D27" s="11" t="n">
         <f aca="false">(Units!C4*it_GB+Units!C5*it_VR+Units!C6*it_RU+Units!C7*it_HP+Units!C8*it_AMDR+Units!C9*it_TPU+Units!C10*it_TRN+Units!C11*it_ASIC)</f>
@@ -22276,12 +23341,12 @@
         <v>2260.39027777778</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>34</v>
@@ -22303,12 +23368,12 @@
         <v>0.170477418783998</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>34</v>
@@ -22332,15 +23397,15 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C32" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_su_sw+Units!B5*c_VR_su_sw+Units!B6*c_RU_su_sw+Units!B7*c_HP_su_sw)/1000+nv_su_ic*(Units!B4*c_GB_su_ic+Units!B5*c_VR_su_ic+Units!B6*c_RU_su_ic+Units!B7*c_HP_su_ic)/1000+nv_so_sw*(Units!B4*c_GB_so_sw+Units!B5*c_VR_so_sw+Units!B6*c_RU_so_sw+Units!B7*c_HP_so_sw)/1000+(Units!B4*c_GB_nic+Units!B5*c_VR_nic+Units!B6*c_RU_nic+Units!B7*c_HP_nic)/1000+nv_opt*(Units!B4*c_GB_so_opt+Units!B5*c_VR_so_opt+Units!B6*c_RU_so_opt+Units!B7*c_HP_so_opt)/1000</f>
@@ -22361,10 +23426,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C33" s="11" t="n">
         <f aca="false">rep_nv26</f>
@@ -22373,7 +23438,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>34</v>
@@ -22385,10 +23450,10 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C35" s="11" t="n">
         <f aca="false">avgo_su*(Units!B8*c_AMD8_su_sw+Units!B9*c_TPU_su_sw+Units!B10*c_TRN_su_sw+Units!B11*c_ASIC_su_sw)/1000+avgo_so*((1-nv_so_sw)*(Units!B4*c_GB_so_sw+Units!B5*c_VR_so_sw+Units!B6*c_RU_so_sw+Units!B7*c_HP_so_sw)/1000+(Units!B8*c_AMD8_so_sw+Units!B9*c_TPU_so_sw+Units!B10*c_TRN_so_sw+Units!B11*c_ASIC_so_sw)/1000)+avgo_nic*(Units!B8*c_AMD8_nic+Units!B9*c_TPU_nic+Units!B10*c_TRN_nic+Units!B11*c_ASIC_nic)/1000+avgo_opt*C18</f>
@@ -22409,10 +23474,10 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C36" s="11" t="n">
         <f aca="false">rep_avgo26</f>
@@ -22421,7 +23486,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>34</v>
@@ -22433,7 +23498,7 @@
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>34</v>
@@ -22455,15 +23520,15 @@
         <v>0.506383309004517</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C39" s="11" t="n">
         <f aca="false">C18</f>
@@ -22474,12 +23539,12 @@
         <v>26</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>34</v>
@@ -22491,12 +23556,12 @@
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>34</v>
@@ -22518,15 +23583,15 @@
         <v>0.16</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C44" s="11" t="n">
         <f aca="false">C8*cpo_A_26</f>
@@ -22547,10 +23612,10 @@
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C45" s="11" t="n">
         <f aca="false">C18-C44</f>
@@ -22569,12 +23634,12 @@
         <v>72.9348</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>34</v>
@@ -22596,15 +23661,15 @@
         <v>0.08</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C47" s="11" t="n">
         <f aca="false">C8*cpo_B_26</f>
@@ -22625,10 +23690,10 @@
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C48" s="11" t="n">
         <f aca="false">C18-C47</f>
@@ -22649,7 +23714,7 @@
     </row>
     <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>34</v>
@@ -22671,15 +23736,15 @@
         <v>0.05</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C50" s="11" t="n">
         <f aca="false">C8*cpo_C_26</f>
@@ -22700,10 +23765,10 @@
     </row>
     <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C51" s="11" t="n">
         <f aca="false">C18-C50</f>
@@ -22724,10 +23789,10 @@
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C52" s="13" t="n">
         <f aca="false">C19-C44</f>
@@ -22771,21 +23836,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22803,7 +23868,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">Mkt!D11-0.3*u_rb_27*(c_VR_su_sw+c_VR_su_ic+c_VR_so_sw+c_VR_so_opt+c_VR_so_cu+c_VR_nic)/1000</f>
@@ -22814,12 +23879,12 @@
         <v>-0.175948810464954</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">Mkt!D11+0.3*u_rb_27*(c_VR_su_sw+c_VR_su_ic+c_VR_so_sw+c_VR_so_opt+c_VR_so_cu+c_VR_nic)/1000</f>
@@ -22832,7 +23897,7 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">Mkt!D11-0.2*u_rb_27*(c_VR_su_sw+c_VR_su_ic+c_VR_so_sw+c_VR_so_opt+c_VR_so_cu+c_VR_nic)/1000</f>
@@ -22845,7 +23910,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">Mkt!D11+0.2*u_rb_27*(c_VR_su_sw+c_VR_su_ic+c_VR_so_sw+c_VR_so_opt+c_VR_so_cu+c_VR_nic)/1000</f>
@@ -22858,7 +23923,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">Mkt!D11+(Units!C9*(c_TPU_su_sw+c_TPU_su_ic+c_TPU_so_sw+c_TPU_so_opt+c_TPU_so_cu+c_TPU_nic)+Units!C10*(c_TRN_su_sw+c_TRN_su_ic+c_TRN_so_sw+c_TRN_so_opt+c_TRN_so_cu+c_TRN_nic)+Units!C11*(c_ASIC_su_sw+c_ASIC_su_ic+c_ASIC_so_sw+c_ASIC_so_opt+c_ASIC_so_cu+c_ASIC_nic))/1000</f>
@@ -22869,7 +23934,7 @@
         <v>0.189775770523822</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -22897,135 +23962,135 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
